--- a/api/templates/critical_errors_by_device/fr.xlsx
+++ b/api/templates/critical_errors_by_device/fr.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harshthakkar/Desktop/Projects/aspect/api/templates/critical_errors_by_device/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AC693E5-3927-1940-A69B-392B9D8E6FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3007C401-9B5D-8E48-9753-027ECA92A870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Errors by Device" sheetId="1" r:id="rId1"/>
@@ -35,7 +30,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="82">
+  <si>
+    <t>Erreurs par appareil</t>
+  </si>
   <si>
     <t>Dates: &lt;Dates&gt;</t>
   </si>
@@ -52,12 +50,45 @@
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Site d'origine identique dans le test et l'échantillon</t>
+  </si>
+  <si>
+    <t>Appareil</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>En série</t>
+  </si>
+  <si>
+    <t>Dernier téléchargement</t>
+  </si>
+  <si>
+    <t>Nombre total de tests exécutés pendant la période</t>
+  </si>
+  <si>
+    <t># Invalide</t>
+  </si>
+  <si>
+    <t># Erreurs</t>
+  </si>
+  <si>
+    <t># Aucun résultat</t>
+  </si>
+  <si>
+    <t>Pourcentage d'erreur</t>
+  </si>
+  <si>
     <t># Errors</t>
   </si>
   <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;serial&gt;</t>
   </si>
   <si>
@@ -245,36 +276,6 @@
   </si>
   <si>
     <t>Signal loss detected in the amplification curve</t>
-  </si>
-  <si>
-    <t>Erreurs par appareil</t>
-  </si>
-  <si>
-    <t>Appareil</t>
-  </si>
-  <si>
-    <t>En série</t>
-  </si>
-  <si>
-    <t>Dernier téléchargement</t>
-  </si>
-  <si>
-    <t>Nombre total de tests exécutés pendant la période</t>
-  </si>
-  <si>
-    <t># Invalide</t>
-  </si>
-  <si>
-    <t># Erreurs</t>
-  </si>
-  <si>
-    <t># Aucun résultat</t>
-  </si>
-  <si>
-    <t>Pourcentage d'erreur</t>
-  </si>
-  <si>
-    <t>Site d'origine identique dans le test et l'échantillon</t>
   </si>
 </sst>
 </file>
@@ -284,11 +285,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -308,11 +310,6 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -353,34 +350,23 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="medium">
+      <right style="thin">
         <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
+      </right>
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -408,13 +394,18 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -423,49 +414,64 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -681,1675 +687,1680 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" customWidth="1"/>
-    <col min="4" max="4" width="16.5" customWidth="1"/>
-    <col min="5" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16.1640625" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="11.1640625" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="14" max="14" width="11.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
+    <row r="1" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
+    <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
+    <row r="3" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
+    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3"/>
+    <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
+    <row r="6" spans="1:14" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3"/>
+    <row r="7" spans="1:14" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="25"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="19"/>
-    </row>
-    <row r="8" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>73</v>
+      <c r="H7" s="3"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="26"/>
+    </row>
+    <row r="8" spans="1:14" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>77</v>
+        <v>11</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="D10" s="3"/>
+      <c r="C9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="D11" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="D12" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="D13" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="D14" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="D15" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="D16" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="4:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="D17" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="5:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="4:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="D18" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="5:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="4:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="D19" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="5:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="4:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="D20" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" spans="5:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D21" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D22" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D23" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D24" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D25" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
-      <c r="H25" s="4"/>
-    </row>
-    <row r="26" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D26" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="4"/>
+    </row>
+    <row r="26" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="4"/>
+    </row>
+    <row r="27" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
-    </row>
-    <row r="28" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D28" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="4"/>
+    </row>
+    <row r="28" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D29" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="4"/>
+    </row>
+    <row r="29" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="4"/>
-    </row>
-    <row r="30" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D30" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="4"/>
-    </row>
-    <row r="31" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D31" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="4"/>
-    </row>
-    <row r="32" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D32" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="4"/>
+    </row>
+    <row r="32" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D33" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="4"/>
+    </row>
+    <row r="33" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D34" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="4"/>
+    </row>
+    <row r="34" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="4"/>
-    </row>
-    <row r="35" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D35" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="4"/>
+    </row>
+    <row r="35" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D36" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="4"/>
+    </row>
+    <row r="36" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D37" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D38" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D39" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="4"/>
+    </row>
+    <row r="39" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D40" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="4"/>
+    </row>
+    <row r="40" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="4"/>
-    </row>
-    <row r="41" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D41" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="4"/>
-    </row>
-    <row r="42" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D42" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="4"/>
+    </row>
+    <row r="42" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="4"/>
-    </row>
-    <row r="43" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D43" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="4"/>
+    </row>
+    <row r="43" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
-      <c r="H43" s="4"/>
-    </row>
-    <row r="44" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D44" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="4"/>
+    </row>
+    <row r="44" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="4"/>
-    </row>
-    <row r="45" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D45" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="4"/>
+    </row>
+    <row r="45" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="4"/>
-    </row>
-    <row r="46" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D46" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="4"/>
+    </row>
+    <row r="46" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D47" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="4"/>
+    </row>
+    <row r="47" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
-      <c r="H47" s="4"/>
-    </row>
-    <row r="48" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D48" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="4"/>
+    </row>
+    <row r="48" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
-      <c r="H48" s="4"/>
-    </row>
-    <row r="49" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D49" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="4"/>
+    </row>
+    <row r="49" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="4"/>
-    </row>
-    <row r="50" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D50" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="4"/>
+    </row>
+    <row r="50" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
-      <c r="H50" s="4"/>
-    </row>
-    <row r="51" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D51" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="4"/>
+    </row>
+    <row r="51" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
-      <c r="H51" s="4"/>
-    </row>
-    <row r="52" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D52" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="4"/>
+    </row>
+    <row r="52" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="4"/>
-    </row>
-    <row r="53" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D53" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="4"/>
+    </row>
+    <row r="53" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="4"/>
-    </row>
-    <row r="54" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D54" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="4"/>
+    </row>
+    <row r="54" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
-      <c r="H54" s="4"/>
-    </row>
-    <row r="55" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D55" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="4"/>
+    </row>
+    <row r="55" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
-      <c r="H55" s="4"/>
-    </row>
-    <row r="56" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D56" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
-      <c r="H56" s="4"/>
-    </row>
-    <row r="57" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D57" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="4"/>
+    </row>
+    <row r="57" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
-      <c r="H57" s="4"/>
-    </row>
-    <row r="58" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D58" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="4"/>
+    </row>
+    <row r="58" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
-      <c r="H58" s="4"/>
-    </row>
-    <row r="59" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D59" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="4"/>
+    </row>
+    <row r="59" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
-      <c r="H59" s="4"/>
-    </row>
-    <row r="60" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D60" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="4"/>
+    </row>
+    <row r="60" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
-      <c r="H60" s="4"/>
-    </row>
-    <row r="61" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D61" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="4"/>
+    </row>
+    <row r="61" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
-      <c r="H61" s="4"/>
-    </row>
-    <row r="62" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D62" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="4"/>
+    </row>
+    <row r="62" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
-      <c r="H62" s="4"/>
-    </row>
-    <row r="63" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D63" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="4"/>
+    </row>
+    <row r="63" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
-      <c r="H63" s="4"/>
-    </row>
-    <row r="64" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D64" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="4"/>
+    </row>
+    <row r="64" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="4"/>
-    </row>
-    <row r="65" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D65" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="4"/>
+    </row>
+    <row r="65" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
-      <c r="H65" s="4"/>
-    </row>
-    <row r="66" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D66" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="4"/>
+    </row>
+    <row r="66" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
-      <c r="H66" s="4"/>
-    </row>
-    <row r="67" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D67" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="4"/>
+    </row>
+    <row r="67" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
-      <c r="H67" s="4"/>
-    </row>
-    <row r="68" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D68" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="4"/>
+    </row>
+    <row r="68" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="4"/>
-    </row>
-    <row r="69" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D69" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="4"/>
+    </row>
+    <row r="69" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
-      <c r="H69" s="4"/>
-    </row>
-    <row r="70" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D70" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="4"/>
+    </row>
+    <row r="70" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
-      <c r="H70" s="4"/>
-    </row>
-    <row r="71" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D71" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="4"/>
+    </row>
+    <row r="71" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="4"/>
-    </row>
-    <row r="72" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D72" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="4"/>
+    </row>
+    <row r="72" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
-      <c r="H72" s="4"/>
-    </row>
-    <row r="73" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D73" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="4"/>
+    </row>
+    <row r="73" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
-      <c r="H73" s="4"/>
-    </row>
-    <row r="74" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D74" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="4"/>
+    </row>
+    <row r="74" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
-      <c r="H74" s="4"/>
-    </row>
-    <row r="75" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D75" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="4"/>
+    </row>
+    <row r="75" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
-      <c r="H75" s="4"/>
-    </row>
-    <row r="76" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D76" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="4"/>
+    </row>
+    <row r="76" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
-      <c r="H76" s="4"/>
-    </row>
-    <row r="77" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D77" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="4"/>
+    </row>
+    <row r="77" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
-      <c r="H77" s="4"/>
-    </row>
-    <row r="78" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D78" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="4"/>
+    </row>
+    <row r="78" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
-      <c r="H78" s="4"/>
-    </row>
-    <row r="79" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D79" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="4"/>
+    </row>
+    <row r="79" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
-      <c r="H79" s="4"/>
-    </row>
-    <row r="80" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D80" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="4"/>
+    </row>
+    <row r="80" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
-      <c r="H80" s="4"/>
-    </row>
-    <row r="81" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D81" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="4"/>
+    </row>
+    <row r="81" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
-      <c r="H81" s="4"/>
-    </row>
-    <row r="82" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D82" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="4"/>
+    </row>
+    <row r="82" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
-      <c r="H82" s="4"/>
-    </row>
-    <row r="83" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D83" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="4"/>
+    </row>
+    <row r="83" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
-      <c r="H83" s="4"/>
-    </row>
-    <row r="84" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D84" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="4"/>
+    </row>
+    <row r="84" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
-      <c r="H84" s="4"/>
-    </row>
-    <row r="85" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D85" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="4"/>
+    </row>
+    <row r="85" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
-      <c r="H85" s="4"/>
-    </row>
-    <row r="86" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D86" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="4"/>
+    </row>
+    <row r="86" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="4"/>
-    </row>
-    <row r="87" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D87" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="4"/>
+    </row>
+    <row r="87" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
-      <c r="H87" s="4"/>
-    </row>
-    <row r="88" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D88" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="4"/>
+    </row>
+    <row r="88" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
-      <c r="H88" s="4"/>
-    </row>
-    <row r="89" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D89" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="4"/>
+    </row>
+    <row r="89" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
-      <c r="H89" s="4"/>
-    </row>
-    <row r="90" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D90" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="4"/>
+    </row>
+    <row r="90" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
-      <c r="H90" s="4"/>
-    </row>
-    <row r="91" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D91" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="4"/>
+    </row>
+    <row r="91" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
-      <c r="H91" s="4"/>
-    </row>
-    <row r="92" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D92" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="4"/>
+    </row>
+    <row r="92" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
-      <c r="H92" s="4"/>
-    </row>
-    <row r="93" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D93" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="4"/>
+    </row>
+    <row r="93" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
-      <c r="H93" s="4"/>
-    </row>
-    <row r="94" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D94" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="4"/>
+    </row>
+    <row r="94" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
-      <c r="H94" s="4"/>
-    </row>
-    <row r="95" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D95" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="4"/>
+    </row>
+    <row r="95" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
-      <c r="H95" s="4"/>
-    </row>
-    <row r="96" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D96" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="4"/>
+    </row>
+    <row r="96" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
-      <c r="H96" s="4"/>
-    </row>
-    <row r="97" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D97" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="4"/>
+    </row>
+    <row r="97" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
-      <c r="H97" s="4"/>
-    </row>
-    <row r="98" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D98" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="4"/>
+    </row>
+    <row r="98" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
-      <c r="H98" s="4"/>
-    </row>
-    <row r="99" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D99" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="4"/>
+    </row>
+    <row r="99" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
-      <c r="H99" s="4"/>
-    </row>
-    <row r="100" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D100" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="4"/>
+    </row>
+    <row r="100" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
-      <c r="H100" s="4"/>
-    </row>
-    <row r="101" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D101" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="4"/>
+    </row>
+    <row r="101" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
-      <c r="H101" s="4"/>
-    </row>
-    <row r="102" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D102" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="4"/>
+    </row>
+    <row r="102" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
-      <c r="H102" s="4"/>
-    </row>
-    <row r="103" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D103" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="4"/>
+    </row>
+    <row r="103" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
-      <c r="H103" s="4"/>
-    </row>
-    <row r="104" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D104" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="4"/>
+    </row>
+    <row r="104" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
-      <c r="H104" s="4"/>
-    </row>
-    <row r="105" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D105" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="4"/>
+    </row>
+    <row r="105" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
-      <c r="H105" s="4"/>
-    </row>
-    <row r="106" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D106" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="4"/>
+    </row>
+    <row r="106" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
-      <c r="H106" s="4"/>
-    </row>
-    <row r="107" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D107" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="4"/>
+    </row>
+    <row r="107" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
-      <c r="H107" s="4"/>
-    </row>
-    <row r="108" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D108" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="4"/>
+    </row>
+    <row r="108" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
-      <c r="H108" s="4"/>
-    </row>
-    <row r="109" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D109" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="4"/>
+    </row>
+    <row r="109" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
-      <c r="H109" s="4"/>
-    </row>
-    <row r="110" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D110" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="4"/>
+    </row>
+    <row r="110" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
-      <c r="H110" s="4"/>
-    </row>
-    <row r="111" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D111" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="4"/>
+    </row>
+    <row r="111" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
-      <c r="H111" s="4"/>
-    </row>
-    <row r="112" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D112" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="4"/>
+    </row>
+    <row r="112" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
-      <c r="H112" s="4"/>
-    </row>
-    <row r="113" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D113" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="4"/>
+    </row>
+    <row r="113" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
-      <c r="H113" s="4"/>
-    </row>
-    <row r="114" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D114" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="4"/>
+    </row>
+    <row r="114" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
-      <c r="H114" s="4"/>
-    </row>
-    <row r="115" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D115" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="4"/>
+    </row>
+    <row r="115" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
-      <c r="H115" s="4"/>
-    </row>
-    <row r="116" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D116" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="4"/>
+    </row>
+    <row r="116" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
-      <c r="H116" s="4"/>
-    </row>
-    <row r="117" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D117" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="4"/>
+    </row>
+    <row r="117" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
-      <c r="H117" s="4"/>
-    </row>
-    <row r="118" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D118" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="4"/>
+    </row>
+    <row r="118" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
-      <c r="H118" s="4"/>
-    </row>
-    <row r="119" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D119" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="4"/>
+    </row>
+    <row r="119" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
-      <c r="H119" s="4"/>
-    </row>
-    <row r="120" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D120" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="4"/>
+    </row>
+    <row r="120" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
-      <c r="H120" s="4"/>
-    </row>
-    <row r="121" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D121" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="4"/>
+    </row>
+    <row r="121" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="3"/>
-      <c r="H121" s="4"/>
-    </row>
-    <row r="122" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D122" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="4"/>
+    </row>
+    <row r="122" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="3"/>
-      <c r="H122" s="4"/>
-    </row>
-    <row r="123" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D123" s="3"/>
+      <c r="H122" s="3"/>
+      <c r="I122" s="4"/>
+    </row>
+    <row r="123" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="3"/>
-      <c r="H123" s="4"/>
-    </row>
-    <row r="124" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D124" s="3"/>
+      <c r="H123" s="3"/>
+      <c r="I123" s="4"/>
+    </row>
+    <row r="124" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="3"/>
-      <c r="H124" s="4"/>
-    </row>
-    <row r="125" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D125" s="3"/>
+      <c r="H124" s="3"/>
+      <c r="I124" s="4"/>
+    </row>
+    <row r="125" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
       <c r="G125" s="3"/>
-      <c r="H125" s="4"/>
-    </row>
-    <row r="126" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D126" s="3"/>
+      <c r="H125" s="3"/>
+      <c r="I125" s="4"/>
+    </row>
+    <row r="126" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
       <c r="G126" s="3"/>
-      <c r="H126" s="4"/>
-    </row>
-    <row r="127" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D127" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="4"/>
+    </row>
+    <row r="127" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
-      <c r="H127" s="4"/>
-    </row>
-    <row r="128" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D128" s="3"/>
+      <c r="H127" s="3"/>
+      <c r="I127" s="4"/>
+    </row>
+    <row r="128" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="3"/>
-      <c r="H128" s="4"/>
-    </row>
-    <row r="129" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D129" s="3"/>
+      <c r="H128" s="3"/>
+      <c r="I128" s="4"/>
+    </row>
+    <row r="129" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3"/>
-      <c r="H129" s="4"/>
-    </row>
-    <row r="130" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D130" s="3"/>
+      <c r="H129" s="3"/>
+      <c r="I129" s="4"/>
+    </row>
+    <row r="130" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="3"/>
-      <c r="H130" s="4"/>
-    </row>
-    <row r="131" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D131" s="3"/>
+      <c r="H130" s="3"/>
+      <c r="I130" s="4"/>
+    </row>
+    <row r="131" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="3"/>
-      <c r="H131" s="4"/>
-    </row>
-    <row r="132" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D132" s="3"/>
+      <c r="H131" s="3"/>
+      <c r="I131" s="4"/>
+    </row>
+    <row r="132" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="3"/>
-      <c r="H132" s="4"/>
-    </row>
-    <row r="133" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D133" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="4"/>
+    </row>
+    <row r="133" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
       <c r="G133" s="3"/>
-      <c r="H133" s="4"/>
-    </row>
-    <row r="134" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D134" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="4"/>
+    </row>
+    <row r="134" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
       <c r="G134" s="3"/>
-      <c r="H134" s="4"/>
-    </row>
-    <row r="135" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D135" s="3"/>
+      <c r="H134" s="3"/>
+      <c r="I134" s="4"/>
+    </row>
+    <row r="135" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
-      <c r="H135" s="4"/>
-    </row>
-    <row r="136" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D136" s="3"/>
+      <c r="H135" s="3"/>
+      <c r="I135" s="4"/>
+    </row>
+    <row r="136" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
       <c r="G136" s="3"/>
-      <c r="H136" s="4"/>
-    </row>
-    <row r="137" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D137" s="3"/>
+      <c r="H136" s="3"/>
+      <c r="I136" s="4"/>
+    </row>
+    <row r="137" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
       <c r="G137" s="3"/>
-      <c r="H137" s="4"/>
-    </row>
-    <row r="138" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D138" s="3"/>
+      <c r="H137" s="3"/>
+      <c r="I137" s="4"/>
+    </row>
+    <row r="138" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
       <c r="G138" s="3"/>
-      <c r="H138" s="4"/>
-    </row>
-    <row r="139" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D139" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="4"/>
+    </row>
+    <row r="139" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
       <c r="G139" s="3"/>
-      <c r="H139" s="4"/>
-    </row>
-    <row r="140" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D140" s="3"/>
+      <c r="H139" s="3"/>
+      <c r="I139" s="4"/>
+    </row>
+    <row r="140" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3"/>
-      <c r="H140" s="4"/>
-    </row>
-    <row r="141" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D141" s="3"/>
+      <c r="H140" s="3"/>
+      <c r="I140" s="4"/>
+    </row>
+    <row r="141" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
       <c r="G141" s="3"/>
-      <c r="H141" s="4"/>
-    </row>
-    <row r="142" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D142" s="3"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="4"/>
+    </row>
+    <row r="142" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
       <c r="G142" s="3"/>
-      <c r="H142" s="4"/>
-    </row>
-    <row r="143" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D143" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="4"/>
+    </row>
+    <row r="143" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
       <c r="G143" s="3"/>
-      <c r="H143" s="4"/>
-    </row>
-    <row r="144" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D144" s="3"/>
+      <c r="H143" s="3"/>
+      <c r="I143" s="4"/>
+    </row>
+    <row r="144" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
       <c r="G144" s="3"/>
-      <c r="H144" s="4"/>
-    </row>
-    <row r="145" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D145" s="3"/>
+      <c r="H144" s="3"/>
+      <c r="I144" s="4"/>
+    </row>
+    <row r="145" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
       <c r="G145" s="3"/>
-      <c r="H145" s="4"/>
-    </row>
-    <row r="146" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D146" s="3"/>
+      <c r="H145" s="3"/>
+      <c r="I145" s="4"/>
+    </row>
+    <row r="146" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
       <c r="G146" s="3"/>
-      <c r="H146" s="4"/>
-    </row>
-    <row r="147" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D147" s="3"/>
+      <c r="H146" s="3"/>
+      <c r="I146" s="4"/>
+    </row>
+    <row r="147" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
       <c r="G147" s="3"/>
-      <c r="H147" s="4"/>
-    </row>
-    <row r="148" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D148" s="3"/>
+      <c r="H147" s="3"/>
+      <c r="I147" s="4"/>
+    </row>
+    <row r="148" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
       <c r="G148" s="3"/>
-      <c r="H148" s="4"/>
-    </row>
-    <row r="149" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D149" s="3"/>
+      <c r="H148" s="3"/>
+      <c r="I148" s="4"/>
+    </row>
+    <row r="149" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
       <c r="G149" s="3"/>
-      <c r="H149" s="4"/>
-    </row>
-    <row r="150" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D150" s="3"/>
+      <c r="H149" s="3"/>
+      <c r="I149" s="4"/>
+    </row>
+    <row r="150" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
       <c r="G150" s="3"/>
-      <c r="H150" s="4"/>
-    </row>
-    <row r="151" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D151" s="3"/>
+      <c r="H150" s="3"/>
+      <c r="I150" s="4"/>
+    </row>
+    <row r="151" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
       <c r="G151" s="3"/>
-      <c r="H151" s="4"/>
-    </row>
-    <row r="152" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D152" s="3"/>
+      <c r="H151" s="3"/>
+      <c r="I151" s="4"/>
+    </row>
+    <row r="152" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="3"/>
-      <c r="H152" s="4"/>
-    </row>
-    <row r="153" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D153" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="I152" s="4"/>
+    </row>
+    <row r="153" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
       <c r="G153" s="3"/>
-      <c r="H153" s="4"/>
-    </row>
-    <row r="154" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D154" s="3"/>
+      <c r="H153" s="3"/>
+      <c r="I153" s="4"/>
+    </row>
+    <row r="154" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
       <c r="G154" s="3"/>
-      <c r="H154" s="4"/>
-    </row>
-    <row r="155" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D155" s="3"/>
+      <c r="H154" s="3"/>
+      <c r="I154" s="4"/>
+    </row>
+    <row r="155" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
-      <c r="H155" s="4"/>
-    </row>
-    <row r="156" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D156" s="3"/>
+      <c r="H155" s="3"/>
+      <c r="I155" s="4"/>
+    </row>
+    <row r="156" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
       <c r="G156" s="3"/>
-      <c r="H156" s="4"/>
-    </row>
-    <row r="157" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D157" s="3"/>
+      <c r="H156" s="3"/>
+      <c r="I156" s="4"/>
+    </row>
+    <row r="157" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
       <c r="G157" s="3"/>
-      <c r="H157" s="4"/>
-    </row>
-    <row r="158" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D158" s="3"/>
+      <c r="H157" s="3"/>
+      <c r="I157" s="4"/>
+    </row>
+    <row r="158" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3"/>
-      <c r="H158" s="4"/>
-    </row>
-    <row r="159" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D159" s="3"/>
+      <c r="H158" s="3"/>
+      <c r="I158" s="4"/>
+    </row>
+    <row r="159" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
-      <c r="H159" s="4"/>
-    </row>
-    <row r="160" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D160" s="3"/>
+      <c r="H159" s="3"/>
+      <c r="I159" s="4"/>
+    </row>
+    <row r="160" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="3"/>
-      <c r="H160" s="4"/>
-    </row>
-    <row r="161" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D161" s="3"/>
+      <c r="H160" s="3"/>
+      <c r="I160" s="4"/>
+    </row>
+    <row r="161" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="3"/>
-      <c r="H161" s="4"/>
-    </row>
-    <row r="162" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D162" s="3"/>
+      <c r="H161" s="3"/>
+      <c r="I161" s="4"/>
+    </row>
+    <row r="162" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
       <c r="G162" s="3"/>
-      <c r="H162" s="4"/>
-    </row>
-    <row r="163" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D163" s="3"/>
+      <c r="H162" s="3"/>
+      <c r="I162" s="4"/>
+    </row>
+    <row r="163" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
       <c r="G163" s="3"/>
-      <c r="H163" s="4"/>
-    </row>
-    <row r="164" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D164" s="3"/>
+      <c r="H163" s="3"/>
+      <c r="I163" s="4"/>
+    </row>
+    <row r="164" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
-      <c r="H164" s="4"/>
-    </row>
-    <row r="165" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D165" s="3"/>
+      <c r="H164" s="3"/>
+      <c r="I164" s="4"/>
+    </row>
+    <row r="165" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3"/>
-      <c r="H165" s="4"/>
-    </row>
-    <row r="166" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D166" s="3"/>
+      <c r="H165" s="3"/>
+      <c r="I165" s="4"/>
+    </row>
+    <row r="166" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
       <c r="G166" s="3"/>
-      <c r="H166" s="4"/>
-    </row>
-    <row r="167" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D167" s="3"/>
+      <c r="H166" s="3"/>
+      <c r="I166" s="4"/>
+    </row>
+    <row r="167" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
       <c r="G167" s="3"/>
-      <c r="H167" s="4"/>
-    </row>
-    <row r="168" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D168" s="3"/>
+      <c r="H167" s="3"/>
+      <c r="I167" s="4"/>
+    </row>
+    <row r="168" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="3"/>
-      <c r="H168" s="4"/>
-    </row>
-    <row r="169" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D169" s="3"/>
+      <c r="H168" s="3"/>
+      <c r="I168" s="4"/>
+    </row>
+    <row r="169" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
-      <c r="H169" s="4"/>
-    </row>
-    <row r="170" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D170" s="3"/>
+      <c r="H169" s="3"/>
+      <c r="I169" s="4"/>
+    </row>
+    <row r="170" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
       <c r="G170" s="3"/>
-      <c r="H170" s="4"/>
-    </row>
-    <row r="171" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D171" s="3"/>
+      <c r="H170" s="3"/>
+      <c r="I170" s="4"/>
+    </row>
+    <row r="171" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="G171" s="3"/>
-      <c r="H171" s="4"/>
-    </row>
-    <row r="172" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D172" s="3"/>
+      <c r="H171" s="3"/>
+      <c r="I171" s="4"/>
+    </row>
+    <row r="172" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="3"/>
-      <c r="H172" s="4"/>
-    </row>
-    <row r="173" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D173" s="3"/>
+      <c r="H172" s="3"/>
+      <c r="I172" s="4"/>
+    </row>
+    <row r="173" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
       <c r="G173" s="3"/>
-      <c r="H173" s="4"/>
-    </row>
-    <row r="174" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D174" s="3"/>
+      <c r="H173" s="3"/>
+      <c r="I173" s="4"/>
+    </row>
+    <row r="174" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
       <c r="G174" s="3"/>
-      <c r="H174" s="4"/>
-    </row>
-    <row r="175" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D175" s="3"/>
+      <c r="H174" s="3"/>
+      <c r="I174" s="4"/>
+    </row>
+    <row r="175" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
       <c r="G175" s="3"/>
-      <c r="H175" s="4"/>
-    </row>
-    <row r="176" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D176" s="3"/>
+      <c r="H175" s="3"/>
+      <c r="I175" s="4"/>
+    </row>
+    <row r="176" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
       <c r="G176" s="3"/>
-      <c r="H176" s="4"/>
-    </row>
-    <row r="177" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D177" s="3"/>
+      <c r="H176" s="3"/>
+      <c r="I176" s="4"/>
+    </row>
+    <row r="177" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
       <c r="G177" s="3"/>
-      <c r="H177" s="4"/>
-    </row>
-    <row r="178" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D178" s="3"/>
+      <c r="H177" s="3"/>
+      <c r="I177" s="4"/>
+    </row>
+    <row r="178" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
       <c r="G178" s="3"/>
-      <c r="H178" s="4"/>
-    </row>
-    <row r="179" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D179" s="3"/>
+      <c r="H178" s="3"/>
+      <c r="I178" s="4"/>
+    </row>
+    <row r="179" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
       <c r="G179" s="3"/>
-      <c r="H179" s="4"/>
-    </row>
-    <row r="180" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D180" s="3"/>
+      <c r="H179" s="3"/>
+      <c r="I179" s="4"/>
+    </row>
+    <row r="180" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
       <c r="G180" s="3"/>
-      <c r="H180" s="4"/>
-    </row>
-    <row r="181" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D181" s="3"/>
+      <c r="H180" s="3"/>
+      <c r="I180" s="4"/>
+    </row>
+    <row r="181" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
       <c r="G181" s="3"/>
-      <c r="H181" s="4"/>
-    </row>
-    <row r="182" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D182" s="3"/>
+      <c r="H181" s="3"/>
+      <c r="I181" s="4"/>
+    </row>
+    <row r="182" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
       <c r="G182" s="3"/>
-      <c r="H182" s="4"/>
-    </row>
-    <row r="183" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D183" s="3"/>
+      <c r="H182" s="3"/>
+      <c r="I182" s="4"/>
+    </row>
+    <row r="183" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
       <c r="G183" s="3"/>
-      <c r="H183" s="4"/>
-    </row>
-    <row r="184" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D184" s="3"/>
+      <c r="H183" s="3"/>
+      <c r="I183" s="4"/>
+    </row>
+    <row r="184" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
       <c r="G184" s="3"/>
-      <c r="H184" s="4"/>
-    </row>
-    <row r="185" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D185" s="3"/>
+      <c r="H184" s="3"/>
+      <c r="I184" s="4"/>
+    </row>
+    <row r="185" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
       <c r="G185" s="3"/>
-      <c r="H185" s="4"/>
-    </row>
-    <row r="186" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D186" s="3"/>
+      <c r="H185" s="3"/>
+      <c r="I185" s="4"/>
+    </row>
+    <row r="186" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
       <c r="G186" s="3"/>
-      <c r="H186" s="4"/>
-    </row>
-    <row r="187" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D187" s="3"/>
+      <c r="H186" s="3"/>
+      <c r="I186" s="4"/>
+    </row>
+    <row r="187" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="G187" s="3"/>
-      <c r="H187" s="4"/>
-    </row>
-    <row r="188" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D188" s="3"/>
+      <c r="H187" s="3"/>
+      <c r="I187" s="4"/>
+    </row>
+    <row r="188" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
       <c r="G188" s="3"/>
-      <c r="H188" s="4"/>
-    </row>
-    <row r="189" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D189" s="3"/>
+      <c r="H188" s="3"/>
+      <c r="I188" s="4"/>
+    </row>
+    <row r="189" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
       <c r="G189" s="3"/>
-      <c r="H189" s="4"/>
-    </row>
-    <row r="190" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D190" s="3"/>
+      <c r="H189" s="3"/>
+      <c r="I189" s="4"/>
+    </row>
+    <row r="190" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E190" s="3"/>
       <c r="F190" s="3"/>
       <c r="G190" s="3"/>
-      <c r="H190" s="4"/>
-    </row>
-    <row r="191" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D191" s="3"/>
+      <c r="H190" s="3"/>
+      <c r="I190" s="4"/>
+    </row>
+    <row r="191" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
       <c r="G191" s="3"/>
-      <c r="H191" s="4"/>
-    </row>
-    <row r="192" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D192" s="3"/>
+      <c r="H191" s="3"/>
+      <c r="I191" s="4"/>
+    </row>
+    <row r="192" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="3"/>
-      <c r="H192" s="4"/>
-    </row>
-    <row r="193" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D193" s="3"/>
+      <c r="H192" s="3"/>
+      <c r="I192" s="4"/>
+    </row>
+    <row r="193" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E193" s="3"/>
       <c r="F193" s="3"/>
       <c r="G193" s="3"/>
-      <c r="H193" s="4"/>
-    </row>
-    <row r="194" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D194" s="3"/>
+      <c r="H193" s="3"/>
+      <c r="I193" s="4"/>
+    </row>
+    <row r="194" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
       <c r="G194" s="3"/>
-      <c r="H194" s="4"/>
-    </row>
-    <row r="195" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D195" s="3"/>
+      <c r="H194" s="3"/>
+      <c r="I194" s="4"/>
+    </row>
+    <row r="195" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
       <c r="G195" s="3"/>
-      <c r="H195" s="4"/>
-    </row>
-    <row r="196" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D196" s="3"/>
+      <c r="H195" s="3"/>
+      <c r="I195" s="4"/>
+    </row>
+    <row r="196" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
       <c r="G196" s="3"/>
-      <c r="H196" s="4"/>
-    </row>
-    <row r="197" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D197" s="3"/>
+      <c r="H196" s="3"/>
+      <c r="I196" s="4"/>
+    </row>
+    <row r="197" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
       <c r="G197" s="3"/>
-      <c r="H197" s="4"/>
-    </row>
-    <row r="198" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D198" s="3"/>
+      <c r="H197" s="3"/>
+      <c r="I197" s="4"/>
+    </row>
+    <row r="198" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E198" s="3"/>
       <c r="F198" s="3"/>
       <c r="G198" s="3"/>
-      <c r="H198" s="4"/>
-    </row>
-    <row r="199" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D199" s="3"/>
+      <c r="H198" s="3"/>
+      <c r="I198" s="4"/>
+    </row>
+    <row r="199" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
       <c r="G199" s="3"/>
-      <c r="H199" s="4"/>
-    </row>
-    <row r="200" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D200" s="3"/>
+      <c r="H199" s="3"/>
+      <c r="I199" s="4"/>
+    </row>
+    <row r="200" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
       <c r="G200" s="3"/>
-      <c r="H200" s="4"/>
-    </row>
-    <row r="201" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D201" s="3"/>
+      <c r="H200" s="3"/>
+      <c r="I200" s="4"/>
+    </row>
+    <row r="201" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
       <c r="G201" s="3"/>
-      <c r="H201" s="4"/>
-    </row>
-    <row r="202" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D202" s="3"/>
+      <c r="H201" s="3"/>
+      <c r="I201" s="4"/>
+    </row>
+    <row r="202" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
       <c r="G202" s="3"/>
-      <c r="H202" s="4"/>
-    </row>
-    <row r="203" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D203" s="3"/>
+      <c r="H202" s="3"/>
+      <c r="I202" s="4"/>
+    </row>
+    <row r="203" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E203" s="3"/>
       <c r="F203" s="3"/>
       <c r="G203" s="3"/>
-      <c r="H203" s="4"/>
-    </row>
-    <row r="204" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D204" s="3"/>
+      <c r="H203" s="3"/>
+      <c r="I203" s="4"/>
+    </row>
+    <row r="204" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
       <c r="G204" s="3"/>
-      <c r="H204" s="4"/>
-    </row>
-    <row r="205" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D205" s="3"/>
+      <c r="H204" s="3"/>
+      <c r="I204" s="4"/>
+    </row>
+    <row r="205" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E205" s="3"/>
       <c r="F205" s="3"/>
       <c r="G205" s="3"/>
-      <c r="H205" s="4"/>
-    </row>
-    <row r="206" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D206" s="3"/>
+      <c r="H205" s="3"/>
+      <c r="I205" s="4"/>
+    </row>
+    <row r="206" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
       <c r="G206" s="3"/>
-      <c r="H206" s="4"/>
-    </row>
-    <row r="207" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D207" s="3"/>
+      <c r="H206" s="3"/>
+      <c r="I206" s="4"/>
+    </row>
+    <row r="207" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E207" s="3"/>
       <c r="F207" s="3"/>
       <c r="G207" s="3"/>
-      <c r="H207" s="4"/>
-    </row>
-    <row r="208" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D208" s="3"/>
+      <c r="H207" s="3"/>
+      <c r="I207" s="4"/>
+    </row>
+    <row r="208" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E208" s="3"/>
       <c r="F208" s="3"/>
       <c r="G208" s="3"/>
-      <c r="H208" s="4"/>
-    </row>
-    <row r="209" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D209" s="3"/>
+      <c r="H208" s="3"/>
+      <c r="I208" s="4"/>
+    </row>
+    <row r="209" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E209" s="3"/>
       <c r="F209" s="3"/>
       <c r="G209" s="3"/>
-      <c r="H209" s="4"/>
-    </row>
-    <row r="210" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D210" s="3"/>
+      <c r="H209" s="3"/>
+      <c r="I209" s="4"/>
+    </row>
+    <row r="210" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E210" s="3"/>
       <c r="F210" s="3"/>
       <c r="G210" s="3"/>
-      <c r="H210" s="4"/>
-    </row>
-    <row r="211" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D211" s="3"/>
+      <c r="H210" s="3"/>
+      <c r="I210" s="4"/>
+    </row>
+    <row r="211" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
       <c r="G211" s="3"/>
-      <c r="H211" s="4"/>
-    </row>
-    <row r="212" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D212" s="3"/>
+      <c r="H211" s="3"/>
+      <c r="I211" s="4"/>
+    </row>
+    <row r="212" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
       <c r="G212" s="3"/>
-      <c r="H212" s="4"/>
-    </row>
-    <row r="213" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D213" s="3"/>
+      <c r="H212" s="3"/>
+      <c r="I212" s="4"/>
+    </row>
+    <row r="213" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E213" s="3"/>
       <c r="F213" s="3"/>
       <c r="G213" s="3"/>
-      <c r="H213" s="4"/>
-    </row>
-    <row r="214" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D214" s="3"/>
+      <c r="H213" s="3"/>
+      <c r="I213" s="4"/>
+    </row>
+    <row r="214" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E214" s="3"/>
       <c r="F214" s="3"/>
       <c r="G214" s="3"/>
-      <c r="H214" s="4"/>
-    </row>
-    <row r="215" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D215" s="3"/>
+      <c r="H214" s="3"/>
+      <c r="I214" s="4"/>
+    </row>
+    <row r="215" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E215" s="3"/>
       <c r="F215" s="3"/>
       <c r="G215" s="3"/>
-      <c r="H215" s="4"/>
-    </row>
-    <row r="216" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D216" s="3"/>
+      <c r="H215" s="3"/>
+      <c r="I215" s="4"/>
+    </row>
+    <row r="216" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
       <c r="G216" s="3"/>
-      <c r="H216" s="4"/>
-    </row>
-    <row r="217" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D217" s="3"/>
+      <c r="H216" s="3"/>
+      <c r="I216" s="4"/>
+    </row>
+    <row r="217" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E217" s="3"/>
       <c r="F217" s="3"/>
       <c r="G217" s="3"/>
-      <c r="H217" s="4"/>
-    </row>
-    <row r="218" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D218" s="3"/>
+      <c r="H217" s="3"/>
+      <c r="I217" s="4"/>
+    </row>
+    <row r="218" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E218" s="3"/>
       <c r="F218" s="3"/>
       <c r="G218" s="3"/>
-      <c r="H218" s="4"/>
-    </row>
-    <row r="219" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D219" s="3"/>
+      <c r="H218" s="3"/>
+      <c r="I218" s="4"/>
+    </row>
+    <row r="219" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E219" s="3"/>
       <c r="F219" s="3"/>
       <c r="G219" s="3"/>
-      <c r="H219" s="4"/>
-    </row>
-    <row r="220" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D220" s="3"/>
+      <c r="H219" s="3"/>
+      <c r="I219" s="4"/>
+    </row>
+    <row r="220" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E220" s="3"/>
       <c r="F220" s="3"/>
       <c r="G220" s="3"/>
-      <c r="H220" s="4"/>
-    </row>
-    <row r="221" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" spans="4:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="H220" s="3"/>
+      <c r="I220" s="4"/>
+    </row>
+    <row r="221" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" spans="5:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3128,29 +3139,30 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="J7:N7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.1640625" customWidth="1"/>
-    <col min="2" max="9" width="9.5" customWidth="1"/>
-    <col min="10" max="10" width="11.1640625" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="11.1640625" customWidth="1"/>
-    <col min="13" max="13" width="33.1640625" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="11" width="11.1640625" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="11.1640625" customWidth="1"/>
+    <col min="14" max="14" width="33.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3165,9 +3177,9 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
     </row>
-    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3182,9 +3194,9 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3199,12 +3211,12 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -3218,12 +3230,12 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -3237,91 +3249,97 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="16">
         <v>5011</v>
       </c>
-      <c r="C9" s="13">
+      <c r="D9" s="16">
         <v>5007</v>
       </c>
-      <c r="D9" s="13">
+      <c r="E9" s="16">
         <v>5006</v>
       </c>
-      <c r="E9" s="13">
+      <c r="F9" s="16">
         <v>2008</v>
       </c>
-      <c r="F9" s="13">
+      <c r="G9" s="16">
         <v>2005</v>
       </c>
-      <c r="G9" s="13">
+      <c r="H9" s="16">
         <v>2037</v>
       </c>
-      <c r="H9" s="13">
+      <c r="I9" s="16">
         <v>2025</v>
       </c>
-      <c r="I9" s="13">
+      <c r="J9" s="16">
         <v>2022</v>
       </c>
-      <c r="J9" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="13" t="s">
+      <c r="K9" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M10" s="3" t="e">
-        <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10+L10</f>
+      <c r="N10" s="13" t="e">
+        <f>C10+D10+E10+F10+G10+H10+I10+J10+K10+L10+M10</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4307,7 +4325,7 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddHeader>&amp;Cffffff&amp;A</oddHeader>
     <oddFooter>&amp;CffffffPage &amp;P</oddFooter>
@@ -4318,7 +4336,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.6640625" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -4326,301 +4344,301 @@
     <col min="4" max="6" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="16">
+    <row r="1" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="19">
         <v>1001</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="16">
+      <c r="B2" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="19">
         <v>1002</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="16">
+      <c r="B3" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="19">
         <v>1004</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="16">
+      <c r="B4" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="19">
         <v>1005</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="B5" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="19">
         <v>1006</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="16">
+      <c r="B6" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="19">
         <v>1007</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="B7" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="19">
         <v>1017</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="16">
+      <c r="B8" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="19">
         <v>1018</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
+      <c r="B9" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="19">
         <v>2003</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="16">
+      <c r="B10" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="19">
         <v>2005</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="16">
+      <c r="B11" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="19">
         <v>2008</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="16">
+      <c r="B12" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="19">
         <v>2009</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="16">
+      <c r="B13" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="19">
         <v>2011</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="16">
+      <c r="B14" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="19">
         <v>2014</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="16">
+      <c r="B15" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="19">
         <v>2016</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="16">
+      <c r="B16" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="19">
         <v>2018</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="16">
+      <c r="B17" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="19">
         <v>2022</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="16">
+      <c r="B18" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="19">
         <v>2025</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="16">
+      <c r="B19" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="19">
         <v>2032</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="B20" s="19" t="s">
         <v>61</v>
       </c>
+      <c r="C20" s="19" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="16">
+      <c r="A21" s="19">
         <v>2034</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>62</v>
+      <c r="B21" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="16">
+      <c r="A22" s="19">
         <v>2037</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>63</v>
+      <c r="B22" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="16">
+      <c r="A23" s="19">
         <v>4010</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>65</v>
+      <c r="B23" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="16">
+      <c r="A24" s="19">
         <v>4017</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>56</v>
+      <c r="B24" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="16">
+      <c r="A25" s="19">
         <v>5006</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>67</v>
+      <c r="B25" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="16">
+      <c r="A26" s="19">
         <v>5007</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>68</v>
+      <c r="B26" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="16">
+      <c r="A27" s="19">
         <v>5011</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>69</v>
+      <c r="B27" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5598,7 +5616,7 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddHeader>&amp;Cffffff&amp;A</oddHeader>
     <oddFooter>&amp;CffffffPage &amp;P</oddFooter>

--- a/api/templates/critical_errors_by_device/fr.xlsx
+++ b/api/templates/critical_errors_by_device/fr.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3007C401-9B5D-8E48-9753-027ECA92A870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9ABFB9-65A4-F94C-9406-5B816ACD9FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Errors by Device" sheetId="1" r:id="rId1"/>
-    <sheet name="Error Codes by Device" sheetId="2" r:id="rId2"/>
+    <sheet name="Erreurs par appareil" sheetId="1" r:id="rId1"/>
+    <sheet name="Codes d'erreur par appareil" sheetId="2" r:id="rId2"/>
     <sheet name="Error Codes" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="81">
   <si>
     <t>Erreurs par appareil</t>
   </si>
@@ -131,9 +131,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Type of error</t>
-  </si>
-  <si>
     <t>Other Error</t>
   </si>
   <si>
@@ -191,91 +188,91 @@
     <t>Run-time error</t>
   </si>
   <si>
-    <t>The actual temperature has drifted too far away from the setpoint</t>
-  </si>
-  <si>
-    <t>The temperature difference exceeds the limit</t>
-  </si>
-  <si>
-    <t>The internal instrument temperature was out of range</t>
-  </si>
-  <si>
-    <t>Optic signal of from detector exceeded the limit</t>
-  </si>
-  <si>
-    <t>Detector dark signal exceeded the limit</t>
-  </si>
-  <si>
-    <t>The power supply was detected to be out of range</t>
-  </si>
-  <si>
-    <t>The measured temperature of the optical system was not within the acceptable range</t>
-  </si>
-  <si>
-    <t>A valve positioning error was detected at the end of the run</t>
-  </si>
-  <si>
     <t>Operation terminated error</t>
   </si>
   <si>
-    <t>Module is already running a test while performing command</t>
-  </si>
-  <si>
-    <t>Motion of the syringe drive was not detected</t>
-  </si>
-  <si>
-    <t>Syringe pressure reading exceeds the protocol limit</t>
-  </si>
-  <si>
-    <t>Syringe pressure reading is below the protocol limit</t>
-  </si>
-  <si>
     <t>Cartridge loading error</t>
   </si>
   <si>
-    <t>Unable to initialize pressure sensor</t>
-  </si>
-  <si>
-    <t>The digital temperature reading for Thermistor A/Thermistor B/Ambient Thermistor/Optic Thermistor was not within the acceptable range</t>
-  </si>
-  <si>
-    <t>The system was unable to find the valve home position</t>
-  </si>
-  <si>
-    <t>Attempt to load a cartridge while the door is still closed</t>
-  </si>
-  <si>
-    <t>Failed to get to desired temperature</t>
-  </si>
-  <si>
-    <t>The system failed to find the plunger home position</t>
-  </si>
-  <si>
-    <t>The ultrasonic horn could not be tuned properly</t>
-  </si>
-  <si>
-    <t>The optical signal from Detector did not reach the expected value</t>
-  </si>
-  <si>
-    <t>The cartridge integrity test failed</t>
-  </si>
-  <si>
     <t>Self-test error</t>
   </si>
   <si>
-    <t>Cooling fan operation was not verified. Measured temperature exceeded the limit</t>
-  </si>
-  <si>
     <t>Post-run analysis error</t>
   </si>
   <si>
-    <t>Probe check failed. Probe check value was above the maximum</t>
-  </si>
-  <si>
-    <t>Probe check failed. Probe check value was below the minimum</t>
-  </si>
-  <si>
-    <t>Signal loss detected in the amplification curve</t>
+    <t>La température réelle s'est trop éloignée du point de consigne</t>
+  </si>
+  <si>
+    <t>La différence de température dépasse la limite</t>
+  </si>
+  <si>
+    <t>La température interne de l'instrument était hors plage</t>
+  </si>
+  <si>
+    <t>Le signal optique du détecteur a dépassé la limite</t>
+  </si>
+  <si>
+    <t>Le signal d'obscurité du détecteur a dépassé la limite</t>
+  </si>
+  <si>
+    <t>L'alimentation électrique a été détectée hors plage</t>
+  </si>
+  <si>
+    <t>La température mesurée du système optique n'était pas dans la plage acceptable</t>
+  </si>
+  <si>
+    <t>Une erreur de positionnement de vanne a été détectée en fin de cycle</t>
+  </si>
+  <si>
+    <t>Le module exécute déjà un test lors de l'exécution d'une commande</t>
+  </si>
+  <si>
+    <t>Le mouvement du piston de la seringue n'a pas été détecté</t>
+  </si>
+  <si>
+    <t>La lecture de pression de la seringue dépasse la limite du protocole</t>
+  </si>
+  <si>
+    <t>La lecture de pression de la seringue est en dessous de la limite du protocole</t>
+  </si>
+  <si>
+    <t>Impossible d'initialiser le capteur de pression</t>
+  </si>
+  <si>
+    <t>La lecture numérique de température pour le Thermistor A / Thermistor B / Thermistor ambiant / Thermistor optique n'était pas dans la plage acceptable</t>
+  </si>
+  <si>
+    <t>Le système n'a pas pu trouver la position initiale de la vanne</t>
+  </si>
+  <si>
+    <t>Tentative de chargement d'une cartouche alors que la porte est encore fermée</t>
+  </si>
+  <si>
+    <t>Échec de l'atteinte de la température souhaitée</t>
+  </si>
+  <si>
+    <t>Le système n'a pas réussi à trouver la position initiale du piston</t>
+  </si>
+  <si>
+    <t>La sonde ultrasonique n'a pas pu être réglée correctement</t>
+  </si>
+  <si>
+    <t>Le signal optique du détecteur n'a pas atteint la valeur attendue</t>
+  </si>
+  <si>
+    <t>Le test d'intégrité de la cartouche a échoué</t>
+  </si>
+  <si>
+    <t>Le fonctionnement du ventilateur de refroidissement n'a pas été vérifié. La température mesurée a dépassé la limite</t>
+  </si>
+  <si>
+    <t>Échec de la vérification de la sonde. La valeur de vérification de la sonde était au-dessus du maximum</t>
+  </si>
+  <si>
+    <t>Échec de la vérification de la sonde. La valeur de vérification de la sonde était en dessous du minimum</t>
+  </si>
+  <si>
+    <t>Perte de signal détectée dans la courbe d'amplification</t>
   </si>
 </sst>
 </file>
@@ -414,7 +411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -448,29 +445,41 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -703,80 +712,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="23"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:14" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="23"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:14" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="25"/>
+      <c r="B7" s="18"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="3"/>
@@ -784,20 +793,20 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
-      <c r="J7" s="20" t="s">
+      <c r="J7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="26"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="20"/>
     </row>
     <row r="8" spans="1:14" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>9</v>
@@ -838,10 +847,10 @@
     </row>
     <row r="9" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>19</v>
@@ -3160,1169 +3169,1170 @@
     <col min="14" max="14" width="33.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14" ht="22" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-    </row>
-    <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+    </row>
+    <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+    </row>
+    <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+    </row>
+    <row r="4" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+    </row>
+    <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="8" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+    </row>
+    <row r="8" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="15" t="s">
+      <c r="B8" s="18"/>
+    </row>
+    <row r="9" spans="1:14" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="26">
+        <v>5011</v>
+      </c>
+      <c r="D9" s="26">
+        <v>5007</v>
+      </c>
+      <c r="E9" s="26">
+        <v>5006</v>
+      </c>
+      <c r="F9" s="26">
+        <v>2008</v>
+      </c>
+      <c r="G9" s="26">
+        <v>2005</v>
+      </c>
+      <c r="H9" s="26">
+        <v>2037</v>
+      </c>
+      <c r="I9" s="26">
+        <v>2025</v>
+      </c>
+      <c r="J9" s="26">
+        <v>2022</v>
+      </c>
+      <c r="K9" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="16">
-        <v>5011</v>
-      </c>
-      <c r="D9" s="16">
-        <v>5007</v>
-      </c>
-      <c r="E9" s="16">
-        <v>5006</v>
-      </c>
-      <c r="F9" s="16">
-        <v>2008</v>
-      </c>
-      <c r="G9" s="16">
-        <v>2005</v>
-      </c>
-      <c r="H9" s="16">
-        <v>2037</v>
-      </c>
-      <c r="I9" s="16">
-        <v>2025</v>
-      </c>
-      <c r="J9" s="16">
-        <v>2022</v>
-      </c>
-      <c r="K9" s="16" t="s">
+      <c r="L9" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="M9" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="N9" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="16" t="s">
+    </row>
+    <row r="10" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="A10" s="27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+      <c r="B10" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="13" t="s">
+      <c r="D10" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="E10" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="F10" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="G10" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="H10" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="I10" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="J10" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="K10" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="L10" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="L10" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="13" t="s">
+      <c r="M10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="N10" s="13" t="e">
+      <c r="N10" s="28" t="e">
         <f>C10+D10+E10+F10+G10+H10+I10+J10+K10+L10+M10</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -4345,300 +4355,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="18" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="16">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="19" t="s">
+      <c r="C2" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="16">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="16">
+        <v>1004</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="16">
+        <v>1005</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="16">
+        <v>1006</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="16">
+        <v>1007</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="16">
+        <v>1017</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="16">
+        <v>1018</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="16">
+        <v>2003</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C10" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="16">
+        <v>2005</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="16">
+        <v>2008</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="16">
+        <v>2009</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="16">
+        <v>2011</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="C14" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="16">
+        <v>2014</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C15" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="16">
+        <v>2016</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="16">
+        <v>2018</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="16">
+        <v>2022</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="16">
+        <v>2032</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="16">
+        <v>2034</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="16">
+        <v>2037</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="16">
+        <v>4010</v>
+      </c>
+      <c r="B23" s="16" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19">
-        <v>1004</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="C23" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="16">
+        <v>4017</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="16">
+        <v>5006</v>
+      </c>
+      <c r="B25" s="16" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19">
-        <v>1005</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
-        <v>1006</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19">
-        <v>1007</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
-        <v>1017</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19">
-        <v>1018</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19">
-        <v>2003</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19">
-        <v>2005</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19">
-        <v>2008</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19">
-        <v>2009</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19">
-        <v>2011</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19">
-        <v>2014</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19">
-        <v>2016</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19">
-        <v>2018</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19">
-        <v>2022</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19">
-        <v>2025</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19">
-        <v>2032</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19">
-        <v>2034</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19">
-        <v>2037</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19">
-        <v>4010</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19">
-        <v>4017</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19">
-        <v>5006</v>
-      </c>
-      <c r="B25" s="19" t="s">
+      <c r="C25" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="19" t="s">
+    </row>
+    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="16">
+        <v>5007</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="16" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19">
-        <v>5007</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="19" t="s">
+    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="16">
+        <v>5011</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="19">
-        <v>5011</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/api/templates/critical_errors_by_device/fr.xlsx
+++ b/api/templates/critical_errors_by_device/fr.xlsx
@@ -400,10 +400,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -447,9 +447,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" shrinkToFit="1"/>
@@ -3178,7 +3175,7 @@
       <c r="M1" s="20"/>
     </row>
     <row r="2" ht="17" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="20"/>
@@ -3195,7 +3192,7 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" ht="17" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="20"/>
@@ -3212,7 +3209,7 @@
       <c r="M3" s="20"/>
     </row>
     <row r="4" ht="17" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
@@ -3231,12 +3228,12 @@
       <c r="M4" s="20"/>
     </row>
     <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="20"/>
@@ -3253,96 +3250,96 @@
       <c r="M6" s="20"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="6"/>
     </row>
     <row r="9" ht="34.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="23">
         <v>5011</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="23">
         <v>5007</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="23">
         <v>5006</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="23">
         <v>2008</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="23">
         <v>2005</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="23">
         <v>2037</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="23">
         <v>2025</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="23">
         <v>2022</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="24" t="s">
+      <c r="L9" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="24" t="s">
+      <c r="M9" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="24" t="s">
+      <c r="N9" s="23" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="26" t="s">
+      <c r="I10" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="26" t="s">
+      <c r="J10" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="26" t="s">
+      <c r="K10" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="L10" s="26" t="s">
+      <c r="L10" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="26" t="e">
+      <c r="N10" s="25" t="e">
         <f>C10+D10+E10+F10+G10+H10+I10+J10+K10+L10+M10</f>
         <v>#VALUE!</v>
       </c>
@@ -4349,299 +4346,299 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
+      <c r="A2" s="27">
         <v>1001</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="27" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="28">
+      <c r="A3" s="27">
         <v>1002</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="27" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
+      <c r="A4" s="27">
         <v>1004</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="27" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="28">
+      <c r="A5" s="27">
         <v>1005</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="27" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
+      <c r="A6" s="27">
         <v>1006</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="27" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
+      <c r="A7" s="27">
         <v>1007</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="27" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
+      <c r="A8" s="27">
         <v>1017</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="27" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+      <c r="A9" s="27">
         <v>1018</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="27" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
+      <c r="A10" s="27">
         <v>2003</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="27" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="28">
+      <c r="A11" s="27">
         <v>2005</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="27" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
+      <c r="A12" s="27">
         <v>2008</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="27" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="28">
+      <c r="A13" s="27">
         <v>2009</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="27" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
+      <c r="A14" s="27">
         <v>2011</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="27" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="28">
+      <c r="A15" s="27">
         <v>2014</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="27" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
+      <c r="A16" s="27">
         <v>2016</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="27" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="28">
+      <c r="A17" s="27">
         <v>2018</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="27" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
+      <c r="A18" s="27">
         <v>2022</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="28">
+      <c r="A19" s="27">
         <v>2025</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="27" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="28">
+      <c r="A20" s="27">
         <v>2032</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="27" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="28">
+      <c r="A21" s="27">
         <v>2034</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="27" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
+      <c r="A22" s="27">
         <v>2037</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="27" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="28">
+      <c r="A23" s="27">
         <v>4010</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="28">
+      <c r="A24" s="27">
         <v>4017</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="27" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="28">
+      <c r="A25" s="27">
         <v>5006</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="27" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="28">
+      <c r="A26" s="27">
         <v>5007</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="28">
+      <c r="A27" s="27">
         <v>5011</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="27" t="s">
         <v>81</v>
       </c>
     </row>

--- a/api/templates/critical_errors_by_device/fr.xlsx
+++ b/api/templates/critical_errors_by_device/fr.xlsx
@@ -33,7 +33,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Dispositifs déclassés: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -403,7 +403,7 @@
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
